--- a/Penilaian_Faithfulness_untuk_Validator.xlsx
+++ b/Penilaian_Faithfulness_untuk_Validator.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Panduan untuk Validator" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Penilaian Faithfulness'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Penilaian Faithfulness'!$A$1:$G$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,12 +47,6 @@
     </font>
     <font>
       <name val="Arial Narrow"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Arial Narrow"/>
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
@@ -60,7 +54,7 @@
       <name val="Arial Narrow"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial Narrow"/>
@@ -92,7 +86,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -116,17 +110,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001565C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001A7A4A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006A1B9A"/>
+        <fgColor rgb="00F57F17"/>
       </patternFill>
     </fill>
     <fill>
@@ -173,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -184,52 +168,46 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -597,18 +575,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -621,7 +597,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Validator: Baca Ground Truth (GT-1 + GT-2) lalu bandingkan dengan Jawaban LLM. Isi skor di kolom KUNING  0.0 = Tidak akurat   |   0.2 = Kurang akurat   |   0.5 = Sebagian benar   |   0.8 = Akurat   |   1.0 = Sangat akurat</t>
+          <t>Petunjuk: Baca Ground Truth 1 DAN Ground Truth 2 pada setiap baris. Beri skor di kolom KUNING untuk masing-masing Ground Truth.  1.0 = Sangat Lengkap &amp; Akurat  |  0.8 = Akurat, kurang detail  |  0.5 = Sebagian benar  |  0.2 = Kurang akurat  |  0.0 = Tidak akurat / tidak relevan</t>
         </is>
       </c>
     </row>
@@ -644,897 +620,574 @@
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Ground Truth 1
-(dari Evaluasi RAG)</t>
+(dari Evaluasi RAG — acuan utama ROUGE/Cosine)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Ground Truth 2
-(dari Literatur Penyakit Padi)</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Jawaban Sistem AI
-(LOW = Qwen2.5-3B  |  MEDIUM = Gemini  |  HIGH = Llama 3.3-70B)</t>
+(dari Literatur Penyakit Padi — BB Padi/IRRI/Kementan)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Skor
+Ground Truth 1
+(ISI VALIDATOR)</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Skor
-[LOW]
-Qwen2.5-3B
+Ground Truth 2
 (ISI VALIDATOR)</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Skor
-[MEDIUM]
-Gemini 2.5 Flash
-(ISI VALIDATOR)</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Skor
-[HIGH]
-Llama 3.3-70B
-(ISI VALIDATOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="370" customHeight="1">
-      <c r="A4" s="7" t="n">
+    </row>
+    <row r="4" ht="190" customHeight="1">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>bacterial_leaf_blight</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Apa gejala dan cara mengatasi hawar daun bakteri pada padi?</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>[bacterial_leaf_blight]
 Hawar Daun Bakteri disebabkan Xanthomonas oryzae pv. oryzae. Gejala: daun menguning dari ujung dan tepi, muncul eksudat kekuningan di pagi hari. Penanganan: semprot bakterisida tembaga (Kocide 77 WP 2-3 g/L), kurangi nitrogen, perbaiki drainase. Pencegahan: varietas tahan (Ciherang, Mekongga), tanam...</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>[bacterial_leaf_blight]
 Gejala: Gejala awal berupa bercak basah dan berminyak pada tepi daun yang kemudian meluas menjadi hawar (blight) berwarna kuning pucat hingga putih keabu-abuan. Gejala berkembang dari ujung dan tepi daun ke arah pangkal. Pada kondisi lembab, eksudat bakteri berwarna kekuningan...
 Penanganan: 1. Pengendalian Kimiawi: Semprot dengan bakterisida berbahan aktif tembaga (copper hydroxide) seperti Kocide 77 WP dosis 2-3 g/L air, atau Agrept 20 WP (streptomycin sulfate) dosis 1-2 g/L air. Lakukan penyemprotan setiap 7-10 hari sekali saat gejala mulai muncul. | 2. Pengendalian Hayati: Aplikasikan Bacillus...</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Oke, saya akan jelaskan tentang hawar daun bakaeri (HDB) ke kita. 
-Gejala HDB:
-- Daun padi tampak merah muda atau hitam sebelum menguning dan lama-lama menjadi abu-abu.
-- Di bagian sisi daun yang bergerigi, Anda akan melihat garis-garis kuning berbentuk seperti noda kecil di antara tulang-tulan...
-[MEDIUM] Gemini 2.5 Flash:
-Halo Pak/Bu Petani!
-Penyakit yang terdeteksi kamera AI adalah Hawar Daun Bakteri. Mari kita bahas dan segera tangani.
-1.  Penjelasan
-[HIGH] Llama 3.3-70B:
-Baik, mari kita bahas tentang Hawar Daun Bakteri (Hawar Daun Bakteri) yang terdeteksi oleh kamera AI.
-1. Penjelasan Singkat: Hawar Daun Bakteri disebabkan oleh bakteri Xanthomonas oryzae pv. oryzae. Gejalanya adalah daun padi yang terinfeksi akan menunjukkan lesi atau bercak yang dapat berkemba...</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr"/>
-      <c r="H4" s="9" t="inlineStr"/>
-      <c r="I4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5" ht="385" customHeight="1">
-      <c r="A5" s="10" t="n">
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="190" customHeight="1">
+      <c r="A5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>leaf_blast</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Tanaman padi saya daunnya ada bercak belah ketupat abu-abu, apa itu dan bagaimana cara mengobatinya?</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>[leaf_blast]
 Blas Daun disebabkan jamur Pyricularia oryzae. Gejala: bercak belah ketupat abu-abu dengan tepi coklat. Penanganan SEGERA: semprot fungisida tricyclazole (Beam 75 WP 0.5-1 g/L) atau isoprothiolane. Kurangi nitrogen, tambah kalium dan silika. Pencegahan: varietas tahan (Inpari 13, 19), hindari nitrog...</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>[leaf_blast]
 Gejala: Lesi berbentuk belah ketupat atau jarum dengan ujung runcing pada kedua sisinya (diamond-shaped lesion). Pusat lesi berwarna abu-abu atau putih dengan tepi berwarna coklat gelap dan zona kuning di sekitarnya (halo). Pada serangan berat, lesi menyatu sehingga daun tampak seperti...
 Penanganan: 1. Pengendalian Kimiawi (Prioritas Utama): Semprot dengan fungisida tricyclazole (Beam 75 WP dosis 0.5-1 g/L air), atau isoprothiolane (Fuji-one 400 EC dosis 1.5-2 ml/L), atau kasugamycin+tembaga (Blascide dosis 2 ml/L). Penyemprotan dilakukan segera saat gejala pertama muncul dan diulang 7-10 hari kemudian. | 2....</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Baik, mari kita bahas soal blas daun:
-Penyakit ini disebabkan oleh jamur Pyricularia oryzae. Jika tidak ditangani, tanaman padi akan mengering dari ujung ke tengah (biasanya terjadi pada 1-4 hari setelah tanam). Tanaman bisa mati jika ada penyakit ini.
-Untuk sekarang:
-1. Cuci tangan Anda dengan sa...
-[MEDIUM] Gemini 2.5 Flash:
-Baik Bapak/Ibu Petani, mari kita bahas penyakit Blas Daun yang terdeteksi pada padi Anda.
-1. Penjelasan Singkat Penyakit Blas Daun:
-P
-[HIGH] Llama 3.3-70B:
-Baik, saya akan membantu petani dengan informasi yang diperlukan.
-1. Penjelasan singkat penyakit Blas Daun (leafblast): Penyakit ini disebabkan oleh jamur Pyricularia oryzae. Gejalanya adalah lesi berbentuk belah ketupat atau jarum pada daun dengan ujung runcing, warna abu-abu atau putih di te...</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr"/>
-      <c r="I5" s="9" t="inlineStr"/>
-    </row>
-    <row r="6" ht="340" customHeight="1">
-      <c r="A6" s="7" t="n">
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="190" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>neck_blast</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Malai padi saya tegak tapi gabahnya hampa, apa penyebabnya dan apa yang harus dilakukan?</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>[neck_blast]
 Blas Leher Malai: jamur Pyricularia oryzae menyerang pangkal malai, menyebabkan gabah hampa total. TINDAKAN DARURAT dalam 24-48 jam: semprot tricyclazole (Beam 75 WP) atau isoprothiolane SEGERA. Hentikan pupuk nitrogen. Pencegahan: semprot preventif 2x (saat primordia + heading 50%).</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>[neck_blast]
 Gejala: Lesi berwarna coklat gelap hingga hitam pada leher malai (node pertama di bawah malai) atau pada buku-buku batang. Jaringan leher malai membusuk sehingga malai patah atau malai menggantung (patah leher). Gabah pada malai yang terinfeksi menjadi hampa, berwarna coklat atau putih...
 Penanganan: 1. TINDAKAN DARURAT - Semprot Segera: Gunakan fungisida tricyclazole (Beam 75 WP dosis 1-1.5 g/L) atau isoprothiolane (Fuji-one 400 EC dosis 2 ml/L) SEGERA saat gejala muncul. Penyemprotan tepat waktu sangat kritis - keterlambatan 3-4 hari dapat menyebabkan kehilangan hasil besar. | 2. Pencegahan pada Primordia:...</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Berdasarkan informasi yang ada, kita akan membahas blas leher malai. Ini adalah penyakit yang sangat berbahaya karena dapat menyebabkan gabah hampir tidak ada.
-Gejala dari blas leher malai:
-- Daun padi tampak seperti terbakar
-- Lesi berbentuk belah ketupat atau jarum dengan ujung runcing
-- Ujung le...
-[MEDIUM] Gemini 2.5 Flash:
-Baik Pak/Bu Tani, berdasarkan deteksi kamera AI, padi Bapak/Ibu saat ini terkena Blas Leher Malai. Mari kita bahas dan cari solusinya bersama.
-[HIGH] Llama 3.3-70B:
-Baik, mari kita bahas tentang Blas Leher Malai (neckblast) yang terdeteksi oleh kamera AI.
-1. Penjelasan Singkat: Blas Leher Malai disebabkan oleh jamur Pyricularia oryzae. Gejalanya adalah lesi berwarna coklat gelap hingga hitam pada leher malai, membuat gabah hampa total dan kehilangan hasil...</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
-    </row>
-    <row r="7" ht="400" customHeight="1">
-      <c r="A7" s="10" t="n">
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="190" customHeight="1">
+      <c r="A7" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>sheath_blight</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Ada lesi abu-abu di pelepah daun bawah tanaman padi saya yang menyebar ke atas, penyakit apa ini?</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>[sheath_blight]
 Busuk Pelepah disebabkan Rhizoctonia solani. Gejala: lesi oval abu-abu pada pelepah daun dekat permukaan air, menyebar ke atas. Penanganan: semprot validamycin (Validacin 3L, 1-2 ml/L) ke pangkal tanaman, kurangi nitrogen, perlebar jarak tanam. Pencegahan: irigasi berselang, hindari tanam rapat.</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>[sheath_blight]
 Gejala: Lesi oval hingga tidak beraturan berwarna hijau abu-abu hingga putih keabu-abuan dengan tepi coklat pada pelepah daun (sheath) dekat permukaan air. Lesi berkembang dari pelepah bawah ke atas menuju daun. Pada kondisi lembab, miselium putih jamur terlihat pada permukaan lesi....
 Penanganan: 1. Pengendalian Kimiawi: Semprot fungisida validamycin (Validacin 3L dosis 1-2 ml/L), hexaconazole (Anvil 50 SC dosis 1 ml/L), atau propiconazole (Tilt 250 EC dosis 0.5 ml/L) langsung ke pangkal tanaman (target pelepah). Penyemprotan volume tinggi (high volume spraying) lebih efektif agar larutan mencapai pangkal...</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Baik, mari kita bicarakan soal Blas Daun. Ini penyakit padi yang cukup berbahaya karena dapat membuat hasil panen hilang secara total jika tak ditangani.
-Penjelasan Singkat:
-Blas Daun disebabkan oleh jamur Pyricularia oryzae. Gejalanya yaitu lesi berbentuk belah ketupat atau jarum dengan ujung ...
-[MEDIUM] Gemini 2.5 Flash:
-Baik Pak/Bu Tani,
-Kamera AI mendeteksi penyakit Busuk Pelepah (sheathblight) pada tanaman padi Bapak/Ibu.
-Mohon maaf, berdasarkan informasi yang saya miliki saat ini, saya tidak menemukan detail spesifik mengenai penyakit Busuk Pelepah (sheath blight) seperti gejala, penyebab, maupun penangan...
-[HIGH] Llama 3.3-70B:
-Baik, saya akan membantu petani dengan informasi tentang penyakit Busuk Pelepah (sheathblight).
-1. Penjelasan singkat penyakit: Busuk Pelepah disebabkan oleh jamur Rhizoctonia solani. Gejala yang umum adalah bercak kecil berwarna abu-abu atau coklat pada pelepah daun, yang kemudian berkembang ...</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr"/>
-      <c r="I7" s="9" t="inlineStr"/>
-    </row>
-    <row r="8" ht="400" customHeight="1">
-      <c r="A8" s="7" t="n">
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="190" customHeight="1">
+      <c r="A8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>tungro</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Daun padi kuning-oranye, tanaman kerdil, bagaimana menanganinya?</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>[tungro]
 Tungro adalah penyakit virus yang disebarkan wereng hijau (Nephotettix virescens). Gejala: daun kuning-oranye dari ujung, tanaman kerdil. Tidak ada obat langsung untuk virus. Penanganan: KENDALIKAN WERENG dengan imidakloprid, cabut dan musnahkan tanaman sakit. Pencegahan: varietas tahan tungro, tana...</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>[tungro]
 Gejala: Daun berwarna kuning hingga kuning-oranye dimulai dari ujung daun, berbeda dengan defisiensi hara yang menguning dari pangkal daun. Tanaman kerdil (stunting) dengan tinggi hanya 1/3 hingga 1/2 dari tanaman normal. Jumlah anakan berkurang drastis. Daun muda menjadi sempit dan...
 Penanganan: 1. PRIORITAS UTAMA - Kendalikan Vektor (Wereng Hijau): Semprot insektisida untuk membunuh wereng: imidakloprid (Confidor 200 SL dosis 0.5 ml/L), buprofezin (Applaud 25 WP dosis 1 g/L), atau BPMC (Bassa 500 EC dosis 2 ml/L). Pengendalian wereng harus dilakukan SEBELUM virus menyebar ke tanaman sehat. | 2. Pencabutan...</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Baiklah, mari kita bahas Blas Daun dan Blas Leher Malai. Keduanya disebabkan oleh jamur sama yaitu Pyricularia oryzae atau Magnaporthe oryzae. Gejala yang muncul bisa jadi berbeda-beda.
-Penyakit: Blas Daun dan Blas Leher Malai
-Gejala pada Blas Daun:
-- Lesi berbentuk seperti jarum di bagian...
-[MEDIUM] Gemini 2.5 Flash:
-Halo Pak/Bu Petani,
-Terima kasih atas informasinya. Kamera AI mendeteksi adanya penyakit Tungro pada padi Bapak/Ibu.
-Namun, saya moh
-[HIGH] Llama 3.3-70B:
-Baik, mari kita bahas tentang penyakit Tungro yang terdeteksi oleh kamera AI.
-1. Penjelasan singkat penyakit Tungro: 
-Tungro adalah penyakit yang disebabkan oleh virus dan ditularkan oleh wereng. Gejala penyakit Tungro antara lain daun yang menguning, kerdil, dan pertumbuhan yang tidak normal. ...</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr"/>
-      <c r="I8" s="9" t="inlineStr"/>
-    </row>
-    <row r="9" ht="385" customHeight="1">
-      <c r="A9" s="10" t="n">
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="190" customHeight="1">
+      <c r="A9" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>brown_spot</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Ada bercak oval coklat dengan pusat putih di daun padi, apa penyakitnya?</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>[brown_spot]
 Bercak Coklat disebabkan Cochliobolus miyabeanus. Gejala: bercak oval coklat dengan pusat abu-abu/putih. Sering terjadi pada lahan defisiensi kalium. Penanganan: fungisida mancozeb (Dithane M-45, 2 g/L) atau propiconazole, tambah pupuk kalium (KCl 50-75 kg/ha). Pencegahan: pemupukan berimbang N-P-K.</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>[brown_spot]
 Gejala: Gejala berupa bercak oval hingga bundar berwarna coklat dengan ukuran 0,5-1 cm pada daun, pelepah, dan gabah. Bercak memiliki pusat berwarna abu-abu atau putih yang dikelilingi cincin berwarna coklat tua hingga ungu kecoklatan. Pada serangan berat, bercak-bercak menyatu sehingga...
 Penanganan: 1. Pengendalian Kimiawi: Semprot dengan fungisida berbahan aktif mancozeb (Dithane M-45 dosis 2 g/L), tricyclazole (Beam 75 WP dosis 0.5-1 g/L), atau propiconazole (Tilt 250 EC dosis 0.5 ml/L). Lakukan penyemprotan 2-3 kali dengan interval 10-14 hari. | 2. Pemupukan: Tambahkan pupuk kalium (KCl) dosis 50-75 kg/ha dan...</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Ya, saya akan membantu Anda mengatasi masalah ini. Berikut adalah langkah-langkah yang harus diambil hari ini:
-Penjelasan Singkat:
-Bercak Coklat adalah penyakit jamur yang membuat daun padi tampak berwarna cokelat kehitaman seperti bercak-bercak kecil. Jamur Cochliobolus miyabeanus adalah pemba...
-[MEDIUM] Gemini 2.5 Flash:
-Baik Bapak/Ibu Petani, mari kita bahas penyakit Bercak Coklat yang terdeteksi ini.
----
-1. Apa Itu Penyakit Bercak Coklat
-[HIGH] Llama 3.3-70B:
-Baik, mari kita bahas tentang penyakit Bercak Coklat (brownspot) pada padi.
-1. Penjelasan Singkat Penyakit: Bercak Coklat disebabkan oleh jamur Cochliobolus miyabeanus. Gejala yang terlihat adalah bercak-bercak coklat pada daun padi. Penyakit ini bisa menyebabkan kerugian hasil panen yang cuku...</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
-    </row>
-    <row r="10" ht="475" customHeight="1">
-      <c r="A10" s="7" t="n">
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="190" customHeight="1">
+      <c r="A10" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>dead_heart</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Pucuk tanaman padi muda mati dan bisa dicabut dengan mudah, apa penyebabnya?</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>[dead_heart]
 Batang Mati/Sundep disebabkan larva penggerek batang (Scirpophaga incertulas). Gejala: pucuk mati kuning-coklat, mudah dicabut, batang dalam berlubang. Penanganan: tabur karbofuran (Furadan 3G 17 kg/ha), atau semprot klorpirifos/fipronil. Lepas parasitoid Trichogramma. Pencegahan: tanam serempak.</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>[dead_heart]
 Gejala: Gejala khas adalah pucuk/tunas yang mati berwarna kuning kecoklatan yang mudah dicabut karena batang bagian dalam telah dimakan larva. Daun tengah tanaman muda layu dan mati sementara daun luar masih hijau. Pada serangan parah, sebagian besar rumpun mengalami kematian pucuk...
 Penanganan: 1. Pengendalian Insektisida: Gunakan insektisida karbofuran (Furadan 3G) dengan cara tabur 17 kg/ha pada saat 7-10 hari setelah tanam. Atau semprot dengan klorpirifos (Dursban 20 EC dosis 2 ml/L), fipronil (Regent 50 SC dosis 0.5-1 ml/L), atau imidakloprid (Confidor 200 SL dosis 0.5 ml/L) pada saat imago (ngengat)...</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Oke, mari kita bahas penyakit ini untuk bantuin padi ya. Penyakit yang saya bicarakan itu disebut Batang Mati (Sundep). Ini terjadi kala pucuk tanaman mati dan tampaknya gara-gara serangga kecil yang namanya penggerek.
-Gejala dan Penyebab
-Gejala penyakit ini:
-- Pucuk/tunas menghitam, mudah dica...
-[MEDIUM] Gemini 2.5 Flash:
-Baik Pak/Bu Tani, mari kita bahas masalah Batang Mati (Sundep) yang terdeteksi pada padi Bapak/Ibu.
----
-1. Penjelasan Singkat Penyakit Batang Mati (Sundep)
-Penyakit ini disebabkan oleh larva penggerek yang masuk dan memakan bagian dalam batang padi.
-Gejala yang bisa Bapak/Ibu l...
-[HIGH] Llama 3.3-70B:
-Baik, mari kita bahas tentang penyakit Batang Mati (Sundep) atau dead heart ini.
-1. Penjelasan singkat: Penyakit ini disebabkan oleh larva yang memakan bagian dalam batang padi, sehingga pucuk tanaman muda mati. Gejala yang terlihat adalah pucuk tanaman berwarna kuning kecoklatan, mudah dicabut...</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="9" t="inlineStr"/>
-      <c r="I10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11" ht="430" customHeight="1">
-      <c r="A11" s="10" t="n">
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="190" customHeight="1">
+      <c r="A11" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>hispa</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Ada goresan putih horizontal di daun padi, kadang ada bagian daun seperti transparan, apa ini?</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>[hispa]
 Hispa Padi disebabkan kumbang Dicladispa armigera. Gejala: goresan putih sejajar dari imago + terowongan transparan (windowing) dari larva. Penanganan: semprot klorpirifos (2 ml/L) atau imidakloprid (0.5 ml/L), celup daun ke air untuk menghilangkan imago. Pencegahan: atur jarak tanam, kurangi nitrog...</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>[hispa]
 Gejala: Kerusakan imago: goresan horizontal berwarna putih sejajar (linear scratches) pada permukaan daun yang memberikan penampilan bergaris-garis putih. Goresan terjadi karena imago memakan klorofil daun dari permukaan atas. Kerusakan larva: blotch atau terowongan berwarna putih...
 Penanganan: 1. Pengendalian Insektisida: Semprot dengan insektisida klorpirifos (Dursban 20 EC dosis 2 ml/L), imidakloprid (Confidor 200 SL dosis 0.5 ml/L), atau deltametrin (Decis 25 EC dosis 0.5-1 ml/L). Penyemprotan pagi hari lebih efektif. | 2. Pengendalian Mekanis: Celupkan daun yang terinfeksi ke dalam air atau usap dengan...</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Kita lihat dulu, bagaimana informasi tentang penyakit hispa padi ini?
-Hispa padi adalah penyakit yang disebabkan oleh serangga kumbang hispa. Kumbang ini memiliki duri di tubuhnya dan menggerek daun dari dalam. Serangga imago (anak dewasa) kemudian bisa mencari tempat lain untuk tinggal dengan meng...
-[MEDIUM] Gemini 2.5 Flash:
-Halo Pak/Bu Petani!
-Berdasarkan deteksi kamera AI, tanaman padi Bapak/Ibu terserang Hispa Padi. Jangan khawatir, mari kita tangani bersama.
-Berikut penjelasannya:
-1.  Apa itu Hispa Padi dan Gejalanya?
-       Penyebab: Penyakit ini disebabkan oleh serangan serangga kecil bernama kumba...
-[HIGH] Llama 3.3-70B:
-Baik, saya akan membantu petani dengan informasi yang jelas dan mudah dipahami.
-1. Penjelasan Singkat Penyakit Hispa Padi: Penyakit Hispa Padi disebabkan oleh serangga kumbang hispa (Dicladispa armigera). Gejala yang terlihat adalah adanya corengan putih pada daun padi karena serangga ini mengg...</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr"/>
-      <c r="I11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="370" customHeight="1">
-      <c r="A12" s="7" t="n">
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="190" customHeight="1">
+      <c r="A12" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>bacterial_panicle_blight</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Malai padi berisi gabah hampa berwarna coklat dan biji mengeriput saat pembungaan, apa ini?</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>[bacterial_panicle_blight]
 Hawar Malai Bakteri disebabkan Burkholderia glumae. Gejala: malai tegak, gabah hampa berwarna coklat/abu, pangkal gabah coklat. Penanganan: semprot kasugamycin (Kasumin 2L, 1-2 ml/L) saat primordia dan 50% pembungaan. Pencegahan: perlakuan benih, hindari nitrogen tinggi menjelang berbunga.</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>[bacterial_panicle_blight]
 Gejala: Gejala utama berupa malai yang berdiri tegak karena gabah hampa (tidak berisi). Biji padi yang terinfeksi berwarna coklat hingga abu-abu dan mengeriput. Infeksi terjadi saat pembungaan, menyebabkan gabah gagal terisi. Pada serangan berat, seluruh malai dapat terlihat hampa dan...
 Penanganan: 1. Pengendalian Kimiawi: Semprot dengan bakterisida berbahan aktif kasugamycin seperti Kasumin 2L dosis 1-2 ml/L air pada saat primordial malai dan awal pembungaan. Atau gunakan oxolinic acid (Staimer 200 EC). | 2. Pengendalian Budidaya: Hindari pemupukan nitrogen berlebih, atur waktu tanam agar pembungaan tidak...</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Baik ya, mari kita bicarakan tentang Hawar Malai Bakteri (HMB), penyakit ini sangat berbahaya bagi hasil panen padi. HMB disebabkan oleh bakteri Burkholderia glumae yang masuk melalui luka atau saat pembungaan.
-Gejala HMB:
-- Malai padi tegak dan hampir tidak memiliki gabah
-- Biji padi berwarna ...
-[MEDIUM] Gemini 2.5 Flash:
-Halo Pak/Bu Petani,
-Mari kita bahas penyakit Hawar Malai Bakteri yang terdeteksi di sawah Bapak/Ibu.
-1. Penjelasan Singkat Penyak
-[HIGH] Llama 3.3-70B:
-Baik, mari kita lihat informasi tentang penyakit yang terdeteksi oleh kamera AI, yaitu Hawar Malai Bakteri (bacterialpanicleblight).
-1. Penjelasan Singkat Penyakit: Hawar Malai Bakteri disebabkan oleh bakteri Burkholderia glumae. Gejalanya adalah malai padi yang berdiri tegak karena gabahnya ...</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="9" t="inlineStr"/>
-      <c r="I12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="430" customHeight="1">
-      <c r="A13" s="10" t="n">
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="190" customHeight="1">
+      <c r="A13" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>leaf_smut</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Daun padi saya tampak bintik-bintik hitam kecil tersebar, tidak terlalu parah, apa itu?</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>[leaf_smut]
 Gosong Palsu Daun disebabkan Entyloma oryzae. Gejala: bercak hitam/abu-abu kecil oval 1-5 mm tersebar di daun, ada serbuk hitam (spora). Penanganan: fungisida tembaga (Kocide 77 WP 2 g/L) atau mancozeb. Penyakit ini umumnya tidak menyebabkan kehilangan hasil besar. Pencegahan: drainase baik, hindari...</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>[leaf_smut]
 Gejala: Bercak-bercak kecil berwarna hitam atau abu-abu gelap berbentuk oval hingga memanjang tersebar pada helai daun. Bercak berukuran 1-5 mm dengan serbuk hitam (spora) di permukaan. Daun yang terinfeksi berat menunjukkan banyak titik-titik hitam yang menyebar di seluruh permukaan...
 Penanganan: 1. Pengendalian Kimiawi: Semprot dengan fungisida tembaga (copper hydroxide) seperti Kocide 77 WP dosis 2 g/L, mancozeb (Dithane M-45 dosis 2 g/L), atau propiconazole (Tilt 250 EC dosis 0.5 ml/L). | 2. Pengendalian Budidaya: Perbaiki drainase, hindari kepadatan tanaman berlebih, dan jaga sirkulasi udara yang baik. |...</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Baiklah, mari kita bicara tentang penyakit Gosong Palsu Daun. Ini adalah penyakit kecil di daun padi yang membuatnya tampak berbusa atau hitam kecil.
-Gejala yang terlihat seperti ini:
-1. Di atas daun akan muncul bercak-bercak hitam atau abu-abu kecil, yang kemudian menjadi lebih besar.
-2. Bercak te...
-[MEDIUM] Gemini 2.5 Flash:
-Baik Pak/Bu Tani, mari kita tangani masalah Gosong Palsu Daun ini.
----
-1. Penjelasan Singkat Penyakit Gosong Palsu Daun
-Penyakit ini disebabkan oleh jamur. Bapak/Ibu bisa melihat gejala di daun padi berupa bercak-bercak kecil berwarna hitam atau abu-abu gelap, bentuknya bisa oval samp...
-[HIGH] Llama 3.3-70B:
-Baik, mari kita bahas tentang penyakit Gosong Palsu Daun (leafsmut) yang terdeteksi oleh kamera AI.
-1. Penjelasan singkat penyakit ini: Penyakit ini disebabkan oleh jamur Entyloma oryzae. Gejala yang terlihat adalah bercak-bercak kecil berwarna hitam atau abu-abu gelap pada daun padi. Berc...</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr"/>
-      <c r="H13" s="9" t="inlineStr"/>
-      <c r="I13" s="9" t="inlineStr"/>
-    </row>
-    <row r="14" ht="325" customHeight="1">
-      <c r="A14" s="7" t="n">
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="190" customHeight="1">
+      <c r="A14" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>downy_mildew</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Ada lapisan putih seperti tepung di bawah daun padi, tanaman terlihat kerdil dan daun distorsi</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>[downy_mildew]
 Embun Bulu disebabkan Sclerophthora macrospora. Gejala: serbuk putih di bawah daun, tanaman kerdil, daun distorsi, kadang malai berubah jadi daun (crazy top). Penanganan: fungisida metalaxil (Ridomil Gold 35 WS, 2 g/L), kurangi genangan air, perbaiki drainase. Pencegahan: seed treatment metalaxil, h...</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>[downy_mildew]
 Gejala: Gejala pada daun berupa lapisan serbuk berwarna putih seperti tepung pada permukaan bawah daun, terutama terlihat pada pagi hari saat embun. Daun yang terinfeksi dapat menunjukkan klorosis (menguning), distorsi, dan pertumbuhan abnormal. Pada serangan sistemik, tanaman...
 Penanganan: 1. Pengendalian Kimiawi: Aplikasikan fungisida sistemik berbahan aktif metalaxil (Ridomil Gold 35 WS dosis 2 g/kg benih untuk seed treatment, atau 2 g/L untuk semprot), atau fosetil-Al (Aliette 80 WP dosis 2 g/L). | 2. Pengelolaan Air: Kurangi genangan air di persemaian dan pertanaman, perbaiki drainase untuk...</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Berdasarkan informasi yang telah saya kumpulkan, ada penyakit bernama Embun Bulu atau Downy Mildew pada padi. Penyakit ini disebabkan oleh oomikete (jenis mikroba) yang tumbuh di lingkungan lembab.
-Gejala utamanya adalah daun padi menjadi gelap dan kusam, mirip dengan bercak-bercak hitam kecoklatan...
-[MEDIUM] Gemini 2.5 Flash:
-Halo Pak/Bu Petani!
-Kamera AI mendeteksi tanaman padi Bapak/Ibu terkena Embun Bulu (Downy Mildew). Jangan khawatir, mari kita pah
-[HIGH] Llama 3.3-70B:
-Baik, saya akan membantu Anda sebagai petani padi untuk mengatasi penyakit Embun Bulu (Downy Mildew) yang terdeteksi oleh kamera AI.
-1. Penjelasan Singkat Penyakit: Embun Bulu disebabkan oleh jamur Sclerophthora macrospora. Penyakit ini menyebabkan tanaman padi menjadi malformasi, seperti tanam...</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr"/>
-      <c r="H14" s="9" t="inlineStr"/>
-      <c r="I14" s="9" t="inlineStr"/>
-    </row>
-    <row r="15" ht="415" customHeight="1">
-      <c r="A15" s="10" t="n">
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="175" customHeight="1">
+      <c r="A15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>healthy</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Tanaman padi saya tampak sehat, daun hijau, tidak ada gejala penyakit, apa yang harus saya lakukan?</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>[healthy]
 Tanaman sehat: daun hijau segar, batang tegak, pertumbuhan normal. Lanjutkan program pemupukan berimbang N-P-K sesuai umur tanaman. Terapkan irigasi berselang untuk hemat air. Lakukan pemantauan rutin setiap 7-10 hari. Tidak diperlukan tindakan pengendalian penyakit. Pertahankan kondisi optimal.</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>[healthy]
 Gejala: Tanaman sehat tidak menunjukkan gejala penyakit. Ciri-ciri visual yang terdeteksi kamera AI: daun berwarna hijau tua mengkilap tanpa bercak, lesi, atau perubahan warna abnormal. Batang kokoh dan tegak, tidak mudah rebah. Pertumbuhan seragam dan sesuai umur tanaman. Malai berisi...
 Penanganan: 1. Lanjutkan pemupukan berimbang N-P-K sesuai umur dan kebutuhan varietas; tidak diperlukan pestisida apapun. | 2. Terapkan sistem irigasi berselang (intermittent irrigation) untuk menghemat air dan mencegah penyakit. | 3. Lakukan pemantauan rutin setiap 7-10 hari untuk deteksi dini hama dan penyakit.</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Berikut solusinya:
-1. Penyakitnya namanya Hispa Padi, atau juga dikenal sebagai kumbang hispa. Kebanyakan daun muda padi mati karena dikekang oleh serangga kecil yang berbulu. Usilannya melempar duri ke daun dari dalam. Serangan ini terjadi pada saat tanaman masih muda.
-2. Langkah pertama adalah m...
-[MEDIUM] Gemini 2.5 Flash:
-Bapak/Ibu petani, kabar gembira! Kamera AI mendeteksi bahwa padi Bapak/Ibu dalam kondisi Tanaman Sehat (healthy). Artinya, padi Bapak/Ibu tumbuh dengan sangat baik dan tidak terserang penyakit.
-Berikut penjelasannya:
-1.  Penjelasan Singkat (Gejala dan Penyebab):
-       Gejala: Tanaman...
-[HIGH] Llama 3.3-70B:
-Baik, mari kita bahas satu per satu:
-1. Penjelasan Singkat: Tanaman padi Anda saat ini sehat, tidak ada gejala penyakit atau serangan hama yang terdeteksi. Ini berarti tanaman Anda memiliki pertumbuhan optimal dengan daun hijau segar, batang tegak, dan perkembangan yang sesuai dengan fase pertu...</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
-    </row>
-    <row r="16" ht="415" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="190" customHeight="1">
+      <c r="A16" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>leaf_blast</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Kelembaban udara sangat tinggi 90%, suhu 26°C, apakah ada risiko penyakit dan apa yang harus dilakukan?</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>[leaf_blast]
 Kondisi sensor (kelembaban &gt;85%, suhu 24-28°C) merupakan kondisi optimal penyebaran Blas Daun. Tindakan preventif segera: semprot fungisida tricyclazole (Beam 75 WP 0.5 g/L) sebagai pencegahan. Periksa daun untuk gejala awal bercak ketupat abu-abu. Kurangi pemupukan nitrogen. Tingkatkan drainase unt...</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>[leaf_blast]
 Gejala: Lesi berbentuk belah ketupat atau jarum dengan ujung runcing pada kedua sisinya (diamond-shaped lesion). Pusat lesi berwarna abu-abu atau putih dengan tepi berwarna coklat gelap dan zona kuning di sekitarnya (halo). Pada serangan berat, lesi menyatu sehingga daun tampak seperti...
 Penanganan: 1. Pengendalian Kimiawi (Prioritas Utama): Semprot dengan fungisida tricyclazole (Beam 75 WP dosis 0.5-1 g/L air), atau isoprothiolane (Fuji-one 400 EC dosis 1.5-2 ml/L), atau kasugamycin+tembaga (Blascide dosis 2 ml/L). Penyemprotan dilakukan segera saat gejala pertama muncul dan diulang 7-10 hari kemudian. | 2....</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Kita akan membahas penyakit Blas Daun, yang sangat merugikan tanaman padi. Ini disebabkan oleh jamur Pyricularia oryzae.
-Gejala-gejalanya adalah lesi berbentuk belah ketupat atau jarum di kedua sisi daun. Ujung lesi bisa kemerahan, putih, coklat gelap atau kuning kehitaman dengan lingkaran hijau di...
-[MEDIUM] Gemini 2.5 Flash:
-Halo Pak/Bu Petani,
-Berdasarkan deteksi kamera AI, tanaman padi Bapak/Ibu terkena Blas Daun. Mari kita bahas:
-1.  Apa itu Blas Daun?
-       Penyebab: Penyakit ini disebabkan oleh jamur bernama Pyricularia oryzae. Jamur ini sangat merusak dan bisa menyebabkan gagal panen total kalau ...
-[HIGH] Llama 3.3-70B:
-Baik, saya akan membantu petani dengan informasi yang jelas dan mudah dipahami.
-1. Penjelasan Singkat Penyakit Blas Daun (Leaf Blast): 
-Penyakit Blas Daun disebabkan oleh jamur Pyricularia oryzae. Gejala yang terlihat adalah lesi berbentuk belah ketupat atau jarum pada daun, dengan warna abu-ab...</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr"/>
-      <c r="H16" s="9" t="inlineStr"/>
-      <c r="I16" s="9" t="inlineStr"/>
-    </row>
-    <row r="17" ht="400" customHeight="1">
-      <c r="A17" s="10" t="n">
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="190" customHeight="1">
+      <c r="A17" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>sheath_blight</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Nitrogen tanah sangat tinggi, suhu 30°C, kelembaban 85%, penyakit apa yang perlu diwaspadai?</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>[sheath_blight]
 Kondisi nitrogen tinggi + suhu 28-32°C + kelembaban &gt;80% adalah kondisi OPTIMAL Busuk Pelepah (Rhizoctonia solani). Tindakan: periksa pelepah daun untuk lesi abu-abu. Kurangi dosis nitrogen SEGERA. Semprot validamycin preventif jika ada gejala awal. Perlebar jarak tanam untuk sirkulasi udara. Gunaka...</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>[sheath_blight]
 Gejala: Lesi oval hingga tidak beraturan berwarna hijau abu-abu hingga putih keabu-abuan dengan tepi coklat pada pelepah daun (sheath) dekat permukaan air. Lesi berkembang dari pelepah bawah ke atas menuju daun. Pada kondisi lembab, miselium putih jamur terlihat pada permukaan lesi....
 Penanganan: 1. Pengendalian Kimiawi: Semprot fungisida validamycin (Validacin 3L dosis 1-2 ml/L), hexaconazole (Anvil 50 SC dosis 1 ml/L), atau propiconazole (Tilt 250 EC dosis 0.5 ml/L) langsung ke pangkal tanaman (target pelepah). Penyemprotan volume tinggi (high volume spraying) lebih efektif agar larutan mencapai pangkal...</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Oke, mari kita bicarakan soal blas daun ini. Ini penyakit padi yang perlu kamu waspadai saat tanaman sudah berumur 1-4 hari.
-Gejala Blas Daun:
-- Daun tampak seperti terbakar karena lesi yang menyatu.
-- Lesi berbentuk belah ketupat dengan ujung runcing. 
-- Pusat lesinya berwarna abu-abu dan tepi...
-[MEDIUM] Gemini 2.5 Flash:
-Baik Bapak/Ibu Petani,
-Terima kasih atas informasinya. Kamera AI mendeteksi adanya penyakit Busuk Pelepah (sheathblight) pada tanaman padi Anda.
-Namun, mohon maaf sekali, berdasarkan data pengetahuan yang saya miliki saat ini, informasi lengkap mengenai penyakit Busuk Pelepah (sheathblight...
-[HIGH] Llama 3.3-70B:
-Baik, saya akan membantu petani dengan informasi tentang penyakit Busuk Pelepah (sheathblight) berdasarkan pengetahuan yang tersedia.
-1. Penjelasan Singkat Penyakit: Busuk Pelepah disebabkan oleh jamur yang menyerang pelepah daun padi, menyebabkan gejala seperti bercak kecil berwarna abu-abu a...</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr"/>
-      <c r="H17" s="9" t="inlineStr"/>
-      <c r="I17" s="9" t="inlineStr"/>
-    </row>
-    <row r="18" ht="430" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="190" customHeight="1">
+      <c r="A18" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>tungro</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Petani melaporkan populasi wereng hijau meningkat, apa yang harus dilakukan untuk mencegah tungro?</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>[tungro]
 Wereng hijau adalah vektor virus tungro. Tindakan SEGERA: semprot insektisida sistemik imidakloprid (Confidor 200 SL 0.5 ml/L) atau buprofezin (Applaud 25 WP 1 g/L) untuk membasmi wereng sebelum virus menyebar. Pasang light trap untuk monitoring. Pertahankan musuh alami. Cabut tanaman bergejala kuni...</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>[tungro]
 Gejala: Daun berwarna kuning hingga kuning-oranye dimulai dari ujung daun, berbeda dengan defisiensi hara yang menguning dari pangkal daun. Tanaman kerdil (stunting) dengan tinggi hanya 1/3 hingga 1/2 dari tanaman normal. Jumlah anakan berkurang drastis. Daun muda menjadi sempit dan...
 Penanganan: 1. PRIORITAS UTAMA - Kendalikan Vektor (Wereng Hijau): Semprot insektisida untuk membunuh wereng: imidakloprid (Confidor 200 SL dosis 0.5 ml/L), buprofezin (Applaud 25 WP dosis 1 g/L), atau BPMC (Bassa 500 EC dosis 2 ml/L). Pengendalian wereng harus dilakukan SEBELUM virus menyebar ke tanaman sehat. | 2. Pencabutan...</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Baik, mari kita bahas penyakit yang ditanyakan: Blas Daun.
-Blas Daun ini disebabkan oleh jamur Pyricularia oryzae. Gejala-gejalanya seperti lesi berbentuk cincin pada daun padi, warna kecoklatan di bagian tepi dan pusatnya. Pada serangan yang parah, daun tampak mati dari pangkal ke ujung.
-Untuk pe...
-[MEDIUM] Gemini 2.5 Flash:
-Halo Pak/Bu Petani,
-Terima kasih atas informasinya. Kamera AI mendeteksi penyakit Tungro pada tanaman padi Anda.
-Namun, saya mohon maaf, berdasarkan informasi basis pengetahuan yang saya miliki saat ini, tidak ada data spesifik mengenai penyakit Tungro. Informasi yang tersedia hanya tentang pe...
-[HIGH] Llama 3.3-70B:
-Baik, saya akan membantu petani dengan informasi yang diperlukan.
-1. Penjelasan Singkat Penyakit Tungro: 
-   - Gejala: Tungro disebabkan oleh virus yang menyerang tanaman padi, menyebabkan daun menjadi kuning atau putih, pertumbuhan tanaman terhambat, dan produksi gabah menurun.
-   - Penyebab: ...</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr"/>
-      <c r="H18" s="9" t="inlineStr"/>
-      <c r="I18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19" ht="310" customHeight="1">
-      <c r="A19" s="10" t="n">
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="190" customHeight="1">
+      <c r="A19" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>bacterial_leaf_streak</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Ada garis-garis sempit kuning di antara tulang daun padi disertai butiran eksudat kekuningan, penyakit apa ini?</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>[bacterial_leaf_streak]
 Hawar Daun Bergaris Bakteri disebabkan Xanthomonas oryzae pv. oryzicola. Gejala: lesi garis-garis sempit kuning di antara tulang daun (interveinal) dengan butiran eksudat kekuningan. Penanganan: semprot bakterisida bismerthiazol (Xanthocide 20 WP 2 g/L) atau copper-based (Cupravit OB 21 2-3 g/L), hi...</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>[bacterial_leaf_streak]
 Gejala: Gejala berupa lesi basah berwarna hijau gelap hingga kuning berbentuk garis-garis sempit yang terbatas di antara tulang daun (interveinal). Lesi kemudian berubah warna menjadi coklat kekuningan dan dapat menyatu membentuk area nekrotik yang lebih luas. Pada kondisi lembab,...
 Penanganan: 1. Pengendalian Kimiawi: Gunakan bakterisida berbahan aktif bismerthiazol seperti Xanthocide 20 WP dosis 2 g/L air, atau copper-based bactericide seperti Cupravit OB 21 dosis 2-3 g/L air. Interval penyemprotan 7-10 hari. | 2. Pengendalian Budidaya: Hindari pemupukan nitrogen berlebihan, perbaiki sirkulasi udara dengan...</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Oke, mari kita bicarakan soal hawar daun bergaris bakteri. Ini penyakit padi yang bikin padi gak panen lagi karena daunnya rusak.
-Gejala: 
-- Daun berubah warna kecoklatan dari bawah dan naik ke atas.
-- Terlihat garis-garis kecil nan kekuningan antara batang daun.  
-- Bisa juga ada air asin yang...
-[MEDIUM] Gemini 2.5 Flash:
-Baik Pak/Bu Tani, mari kita langsung tangani masalah ini. Kamera AI mendeteksi tanaman padi Bapak/Ibu terserang Hawar Daun Bergaris Bakteri.
-[HIGH] Llama 3.3-70B:
-Baik, mari kita bahas tentang Hawar Daun Bergaris Bakteri (Bacterial Leaf Streak) yang terdeteksi oleh kamera AI.
-1. Penjelasan Singkat Penyakit: Hawar Daun Bergaris Bakteri disebabkan oleh bakteri Xanthomonas oryzae pv. oryzicola. Gejala utamanya adalah lesi basah berwarna hijau gelap hingga k...</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr"/>
-      <c r="H19" s="9" t="inlineStr"/>
-      <c r="I19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="385" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="190" customHeight="1">
+      <c r="A20" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>harvest_stage</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Malai padi sudah menunduk dan 80% gabah berwarna kuning keemasan, apakah sudah siap panen dan apa langkahnya?</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>[harvest_stage]
 Padi yang 80-95% gabahnya sudah kuning keemasan dan malai menunduk menandakan fase panen optimal. Ukur kadar air gabah — idealnya 20-25% untuk panen. Jadwalkan panen dalam 3-5 hari ke depan saat cuaca cerah. Lakukan panen pagi/sore hari, rontokkan gabah dalam 24 jam. Keringkan hingga kadar air ≤14% ...</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>[harvest_stage]
 Gejala: Fase panen bukan merupakan penyakit. Ciri-ciri yang terdeteksi kamera AI: 80–95% gabah pada malai telah berwarna kuning keemasan, malai menunduk akibat bobot gabah yang penuh, daun bendera dan daun atas mulai mengering dan berwarna kuning hingga coklat muda. Kadar air gabah...
 Penanganan: 1. Ukur kadar air gabah dengan moisture meter; jika sudah 20–25%, jadwalkan panen dalam 3–5 hari ke depan saat cuaca cerah. | 2. Panen pada pagi hari (06.00–10.00) atau sore hari (15.00–17.00) untuk mengurangi kerontokan dan panas berlebih. | 3. Rontokkan gabah dalam 24 jam setelah panen menggunakan power thresher...</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Oke, mari kita urusi langkah-langkahnya.
-1. Tanaman sudah siap untuk dipanen?
-Bersamaan dengan fase panen, tanaman padi harus tampak sehat, tidak ada serangan hama atau penyakit. Jika Anda melihat:
-- Daun yang hijau dan segar
-- Batang tegak berdiri
-- Tanaman memiliki perkembangan yang normal se...
-[MEDIUM] Gemini 2.5 Flash:
-Halo Pak/Bu Petani!
-Kamera AI sudah mendeteksi tanaman Bapak/Ibu di Fase Panen. Ini kabar baik! Mari kita pastikan dan siapkan panennya hari ini.
-Berikut
-[HIGH] Llama 3.3-70B:
-Petani, kita sudah sampai di fase panen! Mari kita konfirmasi dan lakukan beberapa langkah penting.
-1. Konfirmasi siap panen: Periksa tanaman padi Anda, apakah sudah menunjukkan ciri-ciri seperti malai berisi penuh dengan gabah bernas, daun berwarna hijau tua mengkilap, dan batang kokoh serta t...</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr"/>
-      <c r="H20" s="9" t="inlineStr"/>
-      <c r="I20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21" ht="415" customHeight="1">
-      <c r="A21" s="10" t="n">
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="190" customHeight="1">
+      <c r="A21" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>harvest_stage</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Kelembaban udara 85% saat padi siap panen, apa risiko kualitas gabah dan apa yang harus dilakukan?</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>[harvest_stage]
 Kelembaban udara &gt;80% saat panen meningkatkan risiko busuk gabah (Fusarium, Burkholderia glumae) dan membuat gabah sulit kering secara alami. Gunakan pengeringan mekanis (mechanical dryer 40-43°C) jika cuaca tidak mendukung penjemuran. Rontokkan gabah dalam 24 jam setelah panen. Pastikan kadar air g...</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>[harvest_stage]
 Gejala: Fase panen bukan merupakan penyakit. Ciri-ciri yang terdeteksi kamera AI: 80–95% gabah pada malai telah berwarna kuning keemasan, malai menunduk akibat bobot gabah yang penuh, daun bendera dan daun atas mulai mengering dan berwarna kuning hingga coklat muda. Kadar air gabah...
 Penanganan: 1. Ukur kadar air gabah dengan moisture meter; jika sudah 20–25%, jadwalkan panen dalam 3–5 hari ke depan saat cuaca cerah. | 2. Panen pada pagi hari (06.00–10.00) atau sore hari (15.00–17.00) untuk mengurangi kerontokan dan panas berlebih. | 3. Rontokkan gabah dalam 24 jam setelah panen menggunakan power thresher...</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>[LOW] Qwen2.5-3B:
-Kamu telah melihat bahwa tanaman padi sudah siap untuk dipanen. Sekarang kita akan bicara tentang apa yang perlu dilakukan hari ini, dan bagaimana mengamankan hasil panenmu.
-Langkah-langkah yang harus diambil:
-1. Konfirmasi Tanaman Siap: Dalam fase panen, tanaman padi seharusnya sudah tamp...
-[MEDIUM] Gemini 2.5 Flash:
-Baik Pak/Bu Tani, mari kita siapkan panen padi Bapak/Ibu!
-Berdasarkan informasi dari kamera AI yang mendeteksi tanaman Bapak/Ibu di Fase Panen, berikut adalah langkah-langkah yang bisa kita lakukan hari ini:
-1.  Konfirmasi Tanaman Siap Dipanen (Ciri-ciri Visual):
-       Lihat pada malai p...
-[HIGH] Llama 3.3-70B:
-Baik, mari kita bahas satu per satu:
-1. Tanaman Siap Dipanen: Ciri-ciri visual yang terlihat adalah daun berwarna hijau tua mengkilap tanpa bercak atau lesi, batang kokoh dan tegak, pertumbuhan seragam, dan malai berisi penuh dengan gabah bernas. Jika tanaman padi Anda menunjukkan ciri-ciri ini...</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="9" t="inlineStr"/>
-      <c r="I21" s="9" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
@@ -1556,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1564,7 +1217,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>PANDUAN PENGISIAN LEMBAR PENILAIAN FAITHFULNESS</t>
         </is>
@@ -1575,22 +1228,22 @@
       <c r="B2" t="inlineStr"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>APA YANG DINILAI?</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr"/>
+      <c r="B3" s="11" t="inlineStr"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Faithfulness</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Seberapa akurat jawaban sistem AI dibandingkan dengan jawaban referensi dari literatur pertanian (BB Padi, IRRI, Kementan).</t>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Seberapa lengkap dan akurat isi setiap Ground Truth dibandingkan dengan pengetahuan lapangan (gejala penyakit, nama obat/pestisida, dan cara penanganan yang benar menurut literatur BB Padi, IRRI, Kementan).</t>
         </is>
       </c>
     </row>
@@ -1598,272 +1251,249 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
     </row>
-    <row r="6" ht="55" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>3 TIER LLM
-yang Dievaluasi</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [LOW] → Qwen2.5-3B  (Ollama — qwen2.5:3b (LOW))
-  [MEDIUM] → Gemini 2.5 Flash  (Gemini — gemini-2.5-flash (MEDIUM))
-  [HIGH] → Llama 3.3-70B  (Groq — llama-3.3-70b-versatile (HIGH))</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="5" customHeight="1">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>2 SUMBER
 GROUND TRUTH</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Ground Truth 1</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Jawaban referensi yang dibuat peneliti berdasarkan literatur — digunakan sebagai acuan utama evaluasi otomatis (ROUGE, Cosine Similarity).</t>
         </is>
       </c>
     </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Ground Truth 2</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Ringkasan GEJALA dan PENANGANAN dari file penyakit_padi.txt (BB Padi, IRRI, Kementan). Digunakan sebagai acuan tambahan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="5" customHeight="1">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+    </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Ground Truth 2</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>Ringkasan GEJALA dan PENANGANAN dari file penyakit_padi.txt (BB Padi, IRRI, Kementan). Digunakan sebagai acuan tambahan agar validator dapat menilai dari dua sumber.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="5" customHeight="1">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>CARA MENGISI</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Langkah 1</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Buka sheet 'Penilaian Faithfulness'</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>CARA MENGISI</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr"/>
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Langkah 2</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Baca kolom 'Ground Truth 1' — perhatikan apakah gejala, nama penyakit, nama obat/pestisida, dan langkah penanganan sudah lengkap dan benar</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Langkah 1</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Buka sheet 'Penilaian Faithfulness'</t>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Langkah 3</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Baca kolom 'Ground Truth 2' — bandingkan isinya dengan GT-1 dan pengetahuan lapangan Bapak/Ibu</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Langkah 2</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Baca kolom Ground Truth 1 DAN Ground Truth 2 sebagai referensi bersama</t>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Langkah 4</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Isi skor di kolom KUNING 'Skor GT-1' dan 'Skor GT-2' secara terpisah sesuai kualitas masing-masing</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Langkah 3</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Baca kolom 'Jawaban Sistem AI' — perhatikan label [LOW], [MEDIUM], [HIGH] untuk membedakan jawaban tiap model</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Langkah 4</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>Isi skor di kolom KUNING untuk masing-masing tier (LOW / MEDIUM / HIGH)</t>
-        </is>
-      </c>
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Langkah 5</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Skor GT-1 dan GT-2 boleh berbeda — nilai sesuai kelengkapan dan ketepatan informasi masing-masing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="5" customHeight="1">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>Langkah 5</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Skor boleh berbeda antar tier — nilai sesuai kualitas masing-masing jawaban</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="5" customHeight="1">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>PANDUAN SKOR</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>SANGAT LENGKAP &amp; AKURAT — semua fakta penting ada: nama penyakit, gejala khas, nama obat/pestisida spesifik (beserta dosis), dan langkah penanganan sesuai kondisi lapangan</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>PANDUAN SKOR</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr"/>
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>AKURAT — sebagian besar benar, satu-dua detail kurang spesifik (misal: pestisida disebut tapi tanpa dosis) namun tidak menyesatkan</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>SANGAT AKURAT — semua fakta, nama penyakit, nama obat/pestisida, dan langkah penanganan sesuai dengan kedua referensi</t>
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>SEBAGIAN BENAR — ada informasi penting yang terlewat atau berbeda dari referensi (misal: gejala benar tapi penanganan kurang lengkap)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>AKURAT — sebagian besar benar, satu-dua detail kurang spesifik tapi tidak menyesatkan petani</t>
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>KURANG AKURAT — sebagian besar informasi berbeda, tidak lengkap, atau tidak relevan dengan kondisi lapangan</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>SEBAGIAN BENAR — ada informasi penting yang terlewat atau berbeda dari referensi</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>KURANG AKURAT — sebagian besar informasi berbeda atau tidak lengkap</t>
-        </is>
-      </c>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>TIDAK AKURAT — isi tidak sesuai penyakit yang ditanya, atau informasi yang diberikan salah / menyesatkan petani</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="5" customHeight="1">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>TIDAK AKURAT — jawaban tidak sesuai penyakit yang ditanya, atau informasi yang diberikan salah</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="5" customHeight="1">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>CONTOH PENILAIAN</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr"/>
+      <c r="B24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="55" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Skor 1.0</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>GT menyebut: 'Semprot Kocide 77 WP dosis 2-3 g/L, kurangi nitrogen, perbaiki drainase'
+→ Lengkap: ada nama pestisida, dosis, dan tindakan budidaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="55" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Skor 0.5</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>GT menyebut: 'Jaga kebersihan lahan dan hindari kelembaban tinggi'
+→ Benar tapi tidak menyebut pestisida spesifik atau dosis</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>Skor 1.0</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>Referensi: 'Semprot Kocide 77 WP dosis 2-3 g/L, kurangi nitrogen'
-Jawaban AI: 'Semprot bakterisida Kocide 77 WP dosis 2 g/L, kurangi pupuk urea'
-→ Semua fakta penting ada dan benar</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="55" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Skor 0.5</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Referensi: 'Semprot Kocide 77 WP dosis 2-3 g/L, kurangi nitrogen'
-Jawaban AI: 'Jaga kebersihan lahan dan hindari kelembaban tinggi'
-→ Benar tapi tidak menyebut pestisida spesifik</t>
-        </is>
-      </c>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Skor 0.0</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>GT memberikan penjelasan penyakit lain (tidak relevan dengan query)
+→ Tidak sesuai sama sekali</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="5" customHeight="1">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29" ht="55" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>Skor 0.0</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>Referensi: 'Hawar Daun Bakteri — semprot bakterisida tembaga'
-Jawaban AI: memberikan penanganan untuk penyakit lain
-→ Tidak relevan dengan penyakit yang ditanya</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="5" customHeight="1">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31" ht="55" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>CATATAN</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>• Tidak perlu mengisi seluruh tabel dalam satu waktu — bisa dicicil.
-• Jawaban AI sudah disingkat (max ±350 karakter) untuk kemudahan baca.
-• Kolom Jawaban berisi 3 model sekaligus, dipisah label [LOW]/[MEDIUM]/[HIGH].
-• Baris 'healthy' dan 'harvest_stage' BUKAN penyakit — nilai berdasarkan GT-1 dan GT-2 yang tersedia (penjelasan kondisi &amp; penanganan optimal).
+• Baris 'healthy' dan 'harvest_stage' BUKAN penyakit — nilai berdasarkan kelengkapan panduan pemeliharaan/panen yang tersedia.
+• Jika ada GT yang menurut Bapak/Ibu perlu diperbaiki, beri catatan di sel skor (contoh: '0.5 — gejala kurang spesifik').
 • Setelah selesai, kirimkan kembali file Excel ini ke peneliti.</t>
         </is>
       </c>

--- a/Penilaian_Faithfulness_untuk_Validator.xlsx
+++ b/Penilaian_Faithfulness_untuk_Validator.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10547"/>
+    <workbookView windowWidth="23040" windowHeight="11148"/>
   </bookViews>
   <sheets>
     <sheet name="Penilaian Faithfulness" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="119">
   <si>
     <t>LEMBAR PENILAIAN FAITHFULNESS — Sistem Rekomendasi Penyakit Padi</t>
   </si>
@@ -81,9 +81,6 @@
 Penanganan: 1. Pengendalian Kimiawi: Semprot dengan bakterisida berbahan aktif tembaga (copper hydroxide) seperti Kocide 77 WP dosis 2-3 g/L air, atau Agrept 20 WP (streptomycin sulfate) dosis 1-2 g/L air. Lakukan penyemprotan setiap 7-10 hari sekali saat gejala mulai muncul. | 2. Pengendalian Hayati: Aplikasikan Bacillus subtilis atau Pseudomonas fluorescens sebagai agen hayati dengan dosis 10 g/L air. | 3. Pengendalian Budidaya: Kurangi dosis pupuk nitrogen, perbaiki drainase sawah, tanam varietas tahan...</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>leaf_blast</t>
   </si>
   <si>
@@ -324,6 +321,9 @@
   </si>
   <si>
     <t>s</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>APA YANG DINILAI?</t>
@@ -1686,11 +1686,11 @@
       <c r="E4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>13</v>
+      <c r="F4" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.8</v>
       </c>
     </row>
     <row r="5" ht="231" customHeight="1" spans="1:7">
@@ -1698,22 +1698,22 @@
         <v>2</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>13</v>
+      <c r="F5" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="16">
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" ht="225" customHeight="1" spans="1:7">
@@ -1721,22 +1721,22 @@
         <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="D6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="E6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>13</v>
+      <c r="F6" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" ht="238" customHeight="1" spans="1:7">
@@ -1744,22 +1744,22 @@
         <v>4</v>
       </c>
       <c r="B7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="D7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="E7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>13</v>
+      <c r="F7" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" ht="227" customHeight="1" spans="1:7">
@@ -1767,22 +1767,22 @@
         <v>5</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="D8" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="E8" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>13</v>
+      <c r="F8" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0.8</v>
       </c>
     </row>
     <row r="9" ht="207" customHeight="1" spans="1:7">
@@ -1790,22 +1790,22 @@
         <v>6</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="D9" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="E9" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>13</v>
+      <c r="F9" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="16">
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" ht="219" customHeight="1" spans="1:7">
@@ -1813,22 +1813,22 @@
         <v>7</v>
       </c>
       <c r="B10" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="D10" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="E10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>13</v>
+      <c r="F10" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" ht="241" customHeight="1" spans="1:7">
@@ -1836,22 +1836,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="D11" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="E11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>13</v>
+      <c r="F11" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0.8</v>
       </c>
     </row>
     <row r="12" ht="209" customHeight="1" spans="1:7">
@@ -1859,22 +1859,22 @@
         <v>9</v>
       </c>
       <c r="B12" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="D12" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="E12" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>13</v>
+      <c r="F12" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0.8</v>
       </c>
     </row>
     <row r="13" ht="222" customHeight="1" spans="1:7">
@@ -1882,22 +1882,22 @@
         <v>10</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="D13" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="E13" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>13</v>
+      <c r="F13" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" ht="221" customHeight="1" spans="1:7">
@@ -1905,22 +1905,22 @@
         <v>11</v>
       </c>
       <c r="B14" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="D14" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="E14" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>13</v>
+      <c r="F14" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0.8</v>
       </c>
     </row>
     <row r="15" ht="177" customHeight="1" spans="1:7">
@@ -1928,22 +1928,22 @@
         <v>12</v>
       </c>
       <c r="B15" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="D15" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="E15" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>13</v>
+      <c r="F15" s="16">
+        <v>1</v>
+      </c>
+      <c r="G15" s="16">
+        <v>1</v>
       </c>
     </row>
     <row r="16" ht="226" customHeight="1" spans="1:7">
@@ -1951,22 +1951,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>58</v>
-      </c>
       <c r="E16" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="F16" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G16" s="16">
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" ht="252" customHeight="1" spans="1:7">
@@ -1974,22 +1974,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="18" t="s">
-        <v>60</v>
-      </c>
       <c r="E17" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="F17" s="16">
+        <v>1</v>
+      </c>
+      <c r="G17" s="16">
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="223" customHeight="1" spans="1:7">
@@ -1997,22 +1997,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>62</v>
-      </c>
       <c r="E18" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="F18" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0.8</v>
       </c>
     </row>
     <row r="19" ht="216" customHeight="1" spans="1:7">
@@ -2020,22 +2020,22 @@
         <v>16</v>
       </c>
       <c r="B19" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="D19" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="E19" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>13</v>
+      <c r="F19" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="G19" s="16">
+        <v>0.8</v>
       </c>
     </row>
     <row r="20" ht="198" customHeight="1" spans="1:7">
@@ -2043,22 +2043,22 @@
         <v>17</v>
       </c>
       <c r="B20" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D20" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="E20" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>13</v>
+      <c r="F20" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="G20" s="16">
+        <v>0.8</v>
       </c>
     </row>
     <row r="21" ht="197" customHeight="1" spans="1:7">
@@ -2066,56 +2066,56 @@
         <v>18</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C21" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="18" t="s">
-        <v>72</v>
-      </c>
       <c r="E21" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>13</v>
+        <v>69</v>
+      </c>
+      <c r="F21" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G21" s="16">
+        <v>0.5</v>
       </c>
     </row>
     <row r="22" ht="8" customHeight="1"/>
     <row r="23" ht="22" customHeight="1" spans="1:7">
       <c r="A23" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" ht="90" customHeight="1" spans="1:7">
       <c r="A24" s="20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1"/>
     <row r="28" ht="20" customHeight="1" spans="1:7">
       <c r="E28" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:7">
       <c r="E29" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1"/>
     <row r="31" ht="20" customHeight="1"/>
     <row r="32" ht="20" customHeight="1" spans="1:7">
       <c r="E32" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" spans="5:5">
       <c r="E33" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2151,15 +2151,15 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" ht="5" customHeight="1" spans="1:2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2">
@@ -2167,7 +2167,7 @@
         <v>80</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" ht="39" customHeight="1" spans="1:2">
@@ -2180,10 +2180,10 @@
     </row>
     <row r="5" ht="5" customHeight="1" spans="1:2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2">
@@ -2191,7 +2191,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2">
@@ -2212,10 +2212,10 @@
     </row>
     <row r="9" ht="5" customHeight="1" spans="1:2">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2">
@@ -2223,7 +2223,7 @@
         <v>88</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="16" ht="5" customHeight="1" spans="1:2">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:2">
@@ -2279,7 +2279,7 @@
         <v>99</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:2">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="23" ht="5" customHeight="1" spans="1:2">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:2">
@@ -2335,7 +2335,7 @@
         <v>110</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" ht="55" customHeight="1" spans="1:2">
@@ -2364,10 +2364,10 @@
     </row>
     <row r="28" ht="5" customHeight="1" spans="1:2">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" ht="123" customHeight="1" spans="1:2">
